--- a/public/uploads/project-docs/kis-ai-trader-planning.xlsx
+++ b/public/uploads/project-docs/kis-ai-trader-planning.xlsx
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L5" s="768" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="L6" s="768" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="L7" s="788" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       <c r="K4" s="681" t="n"/>
       <c r="L4" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M4" s="817" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="N4" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       <c r="K5" s="681" t="n"/>
       <c r="L5" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M5" s="820" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="N5" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       <c r="K6" s="681" t="n"/>
       <c r="L6" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M6" s="822" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N6" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       <c r="K7" s="681" t="n"/>
       <c r="L7" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M7" s="820" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="N7" s="768" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="N8" s="788" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="N9" s="788" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
